--- a/research/traditional_assets/database/data/denmark/denmark_software_internet.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_software_internet.xlsx
@@ -587,23 +587,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.00622</v>
+      </c>
       <c r="G2">
-        <v>-0.7934839726747243</v>
+        <v>-1.109985528219971</v>
       </c>
       <c r="H2">
-        <v>-1.317919075144509</v>
+        <v>-1.9616497829233</v>
       </c>
       <c r="I2">
-        <v>-1.39253809774041</v>
+        <v>-1.625180897250362</v>
       </c>
       <c r="J2">
-        <v>-1.39253809774041</v>
+        <v>-1.625180897250362</v>
       </c>
       <c r="K2">
-        <v>-2.006</v>
+        <v>-1.862</v>
       </c>
       <c r="L2">
-        <v>-1.054125065685759</v>
+        <v>-1.347322720694645</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.52</v>
+        <v>1.906</v>
       </c>
       <c r="V2">
-        <v>0.41073512252042</v>
+        <v>0.3905737704918033</v>
       </c>
       <c r="W2">
-        <v>-0.3559199699064278</v>
+        <v>-0.2660615049228955</v>
       </c>
       <c r="X2">
-        <v>0.0613741700122322</v>
+        <v>0.1192050628480912</v>
       </c>
       <c r="Y2">
-        <v>-0.41729413991866</v>
+        <v>-0.3852665677709867</v>
       </c>
       <c r="Z2">
-        <v>0.688245931283906</v>
+        <v>0.3431835112987336</v>
       </c>
       <c r="AA2">
-        <v>-0.9393600799242824</v>
+        <v>-0.6065239313646957</v>
       </c>
       <c r="AB2">
-        <v>0.05929090706740586</v>
+        <v>0.112891052772945</v>
       </c>
       <c r="AC2">
-        <v>-0.9986509869916882</v>
+        <v>-0.7194149841376407</v>
       </c>
       <c r="AD2">
-        <v>0.797</v>
+        <v>0.705</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.797</v>
+        <v>0.705</v>
       </c>
       <c r="AG2">
-        <v>-2.723</v>
+        <v>-1.201</v>
       </c>
       <c r="AH2">
-        <v>0.08508594000213515</v>
+        <v>0.126230975828111</v>
       </c>
       <c r="AI2">
-        <v>0.1056048761097125</v>
+        <v>0.1187868576242628</v>
       </c>
       <c r="AJ2">
-        <v>-0.46570891055242</v>
+        <v>-0.3264474041859201</v>
       </c>
       <c r="AK2">
-        <v>-0.6761857462130618</v>
+        <v>-0.2980888557954828</v>
       </c>
       <c r="AL2">
-        <v>0.021</v>
+        <v>0.047</v>
       </c>
       <c r="AM2">
-        <v>-0.01400000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="AN2">
-        <v>-0.3044308632543927</v>
+        <v>-0.316001792917974</v>
       </c>
       <c r="AO2">
-        <v>-126.1904761904762</v>
+        <v>-47.78723404255319</v>
       </c>
       <c r="AP2">
-        <v>1.040106951871658</v>
+        <v>0.5383236216943076</v>
       </c>
       <c r="AQ2">
-        <v>189.2857142857142</v>
+        <v>-102.0909090909091</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +715,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.00622</v>
+      </c>
       <c r="G3">
-        <v>-0.2073684210526316</v>
+        <v>-0.3153284671532847</v>
       </c>
       <c r="H3">
-        <v>-0.4357894736842105</v>
+        <v>-0.6795620437956205</v>
       </c>
       <c r="I3">
-        <v>-0.4526315789473684</v>
+        <v>-0.6905109489051094</v>
       </c>
       <c r="J3">
-        <v>-0.4526315789473684</v>
+        <v>-0.6905109489051094</v>
       </c>
       <c r="K3">
-        <v>-0.296</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.1557894736842105</v>
+        <v>-0.4102189781021898</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.27</v>
+        <v>0.997</v>
       </c>
       <c r="V3">
-        <v>0.1778711484593838</v>
+        <v>0.2694594594594594</v>
       </c>
       <c r="W3">
-        <v>-0.09673202614379084</v>
+        <v>-0.1918088737201365</v>
       </c>
       <c r="X3">
-        <v>0.06330461269645693</v>
+        <v>0.1247667358326779</v>
       </c>
       <c r="Y3">
-        <v>-0.1600366388402478</v>
+        <v>-0.3165756095528144</v>
       </c>
       <c r="Z3">
-        <v>1.478599221789883</v>
+        <v>0.5575905575905575</v>
       </c>
       <c r="AA3">
-        <v>-0.6692607003891051</v>
+        <v>-0.3850223850223849</v>
       </c>
       <c r="AB3">
-        <v>0.05913808680680424</v>
+        <v>0.1121387156823855</v>
       </c>
       <c r="AC3">
-        <v>-0.7283987871959093</v>
+        <v>-0.4971611007047704</v>
       </c>
       <c r="AD3">
-        <v>0.797</v>
+        <v>0.705</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.797</v>
+        <v>0.705</v>
       </c>
       <c r="AG3">
-        <v>-0.473</v>
+        <v>-0.292</v>
       </c>
       <c r="AH3">
-        <v>0.1004157742219983</v>
+        <v>0.1600454029511918</v>
       </c>
       <c r="AI3">
-        <v>0.2138449154816206</v>
+        <v>0.2577696526508227</v>
       </c>
       <c r="AJ3">
-        <v>-0.07094645267736613</v>
+        <v>-0.08568075117370892</v>
       </c>
       <c r="AK3">
-        <v>-0.1925111925111925</v>
+        <v>-0.1680092059838896</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.034</v>
       </c>
       <c r="AM3">
-        <v>-0.023</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0.96256038647343</v>
+        <v>-0.7572502685284639</v>
       </c>
       <c r="AO3">
-        <v>-71.66666666666666</v>
+        <v>-27.8235294117647</v>
       </c>
       <c r="AP3">
-        <v>0.571256038647343</v>
+        <v>0.313641245972073</v>
       </c>
       <c r="AQ3">
-        <v>37.39130434782608</v>
+        <v>-105.1111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -838,22 +844,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-372</v>
+        <v>-91.83333333333331</v>
       </c>
       <c r="H4">
-        <v>-560</v>
+        <v>-148.3333333333333</v>
       </c>
       <c r="I4">
-        <v>-596.6666666666666</v>
+        <v>-108.3333333333333</v>
       </c>
       <c r="J4">
-        <v>-596.6666666666666</v>
+        <v>-108.3333333333333</v>
       </c>
       <c r="K4">
-        <v>-1.71</v>
+        <v>-1.3</v>
       </c>
       <c r="L4">
-        <v>-570</v>
+        <v>-108.3333333333333</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,31 +883,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>0.909</v>
       </c>
       <c r="V4">
-        <v>1.573426573426574</v>
+        <v>0.7703389830508475</v>
       </c>
       <c r="W4">
-        <v>-0.6151079136690648</v>
+        <v>-0.3403141361256545</v>
       </c>
       <c r="X4">
-        <v>0.05944372732800747</v>
+        <v>0.1136433898635046</v>
       </c>
       <c r="Y4">
-        <v>-0.6745516409970723</v>
+        <v>-0.4539575259891591</v>
       </c>
       <c r="Z4">
-        <v>0.002027027027027028</v>
+        <v>0.007643312101910829</v>
       </c>
       <c r="AA4">
-        <v>-1.20945945945946</v>
+        <v>-0.8280254777070065</v>
       </c>
       <c r="AB4">
-        <v>0.05944372732800747</v>
+        <v>0.1136433898635046</v>
       </c>
       <c r="AC4">
-        <v>-1.268903186787467</v>
+        <v>-0.941668867570511</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -913,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-2.25</v>
+        <v>-0.909</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -922,28 +928,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>2.74390243902439</v>
+        <v>-3.354243542435426</v>
       </c>
       <c r="AK4">
-        <v>-1.43312101910828</v>
+        <v>-0.3967699694456568</v>
       </c>
       <c r="AL4">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="AM4">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="AN4">
         <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-198.8888888888889</v>
+        <v>-100</v>
       </c>
       <c r="AP4">
-        <v>1.256983240223464</v>
+        <v>0.6992307692307692</v>
       </c>
       <c r="AQ4">
-        <v>-198.8888888888889</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_software_internet.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_software_internet.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00622</v>
+        <v>0.37765</v>
       </c>
       <c r="G2">
-        <v>-1.109985528219971</v>
+        <v>-0.7002652519893898</v>
       </c>
       <c r="H2">
-        <v>-1.9616497829233</v>
+        <v>-1.830238726790451</v>
       </c>
       <c r="I2">
-        <v>-1.625180897250362</v>
+        <v>-1.813439434129089</v>
       </c>
       <c r="J2">
-        <v>-1.625180897250362</v>
+        <v>-1.813439434129089</v>
       </c>
       <c r="K2">
-        <v>-1.862</v>
+        <v>-1.905</v>
       </c>
       <c r="L2">
-        <v>-1.347322720694645</v>
+        <v>-1.684350132625995</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.906</v>
+        <v>0.6859999999999999</v>
       </c>
       <c r="V2">
-        <v>0.3905737704918033</v>
+        <v>0.2810323637853339</v>
       </c>
       <c r="W2">
-        <v>-0.2660615049228955</v>
+        <v>-0.3773552955665025</v>
       </c>
       <c r="X2">
-        <v>0.1192050628480912</v>
+        <v>0.1058309561602778</v>
       </c>
       <c r="Y2">
-        <v>-0.3852665677709867</v>
+        <v>-0.4831862517267803</v>
       </c>
       <c r="Z2">
-        <v>0.3431835112987336</v>
+        <v>0.2807148175725986</v>
       </c>
       <c r="AA2">
-        <v>-0.6065239313646957</v>
+        <v>-0.5302567358438157</v>
       </c>
       <c r="AB2">
-        <v>0.112891052772945</v>
+        <v>0.09560419126932176</v>
       </c>
       <c r="AC2">
-        <v>-0.7194149841376407</v>
+        <v>-0.6258609271131375</v>
       </c>
       <c r="AD2">
-        <v>0.705</v>
+        <v>0.725</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.705</v>
+        <v>0.725</v>
       </c>
       <c r="AG2">
-        <v>-1.201</v>
+        <v>0.03900000000000003</v>
       </c>
       <c r="AH2">
-        <v>0.126230975828111</v>
+        <v>0.2289955780164245</v>
       </c>
       <c r="AI2">
-        <v>0.1187868576242628</v>
+        <v>0.1699882766705745</v>
       </c>
       <c r="AJ2">
-        <v>-0.3264474041859201</v>
+        <v>0.01572580645161292</v>
       </c>
       <c r="AK2">
-        <v>-0.2980888557954828</v>
+        <v>0.01089689857502097</v>
       </c>
       <c r="AL2">
-        <v>0.047</v>
+        <v>0.061</v>
       </c>
       <c r="AM2">
-        <v>0.022</v>
+        <v>0.03899999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.316001792917974</v>
+        <v>-0.3557409224730128</v>
       </c>
       <c r="AO2">
-        <v>-47.78723404255319</v>
+        <v>-33.62295081967213</v>
       </c>
       <c r="AP2">
-        <v>0.5383236216943076</v>
+        <v>-0.01913640824337588</v>
       </c>
       <c r="AQ2">
-        <v>-102.0909090909091</v>
+        <v>-52.58974358974361</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seluxit A/S (CPSE:SLXIT)</t>
+          <t>Conferize A/S (CPSE:CONFRZ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00622</v>
+        <v>0.772</v>
       </c>
       <c r="G3">
-        <v>-0.3153284671532847</v>
+        <v>-4.451612903225807</v>
       </c>
       <c r="H3">
-        <v>-0.6795620437956205</v>
+        <v>-28.70967741935484</v>
       </c>
       <c r="I3">
-        <v>-0.6905109489051094</v>
+        <v>-27.7741935483871</v>
       </c>
       <c r="J3">
-        <v>-0.6905109489051094</v>
+        <v>-27.7741935483871</v>
       </c>
       <c r="K3">
-        <v>-0.5620000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="L3">
-        <v>-0.4102189781021898</v>
+        <v>-32.90322580645162</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.997</v>
+        <v>0.283</v>
       </c>
       <c r="V3">
-        <v>0.2694594594594594</v>
+        <v>0.487091222030981</v>
       </c>
       <c r="W3">
-        <v>-0.1918088737201365</v>
+        <v>-0.31875</v>
       </c>
       <c r="X3">
-        <v>0.1247667358326779</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="Y3">
-        <v>-0.3165756095528144</v>
+        <v>-0.4157357792360829</v>
       </c>
       <c r="Z3">
-        <v>0.5575905575905575</v>
+        <v>0.0135312090790048</v>
       </c>
       <c r="AA3">
-        <v>-0.3850223850223849</v>
+        <v>-0.375818419903972</v>
       </c>
       <c r="AB3">
-        <v>0.1121387156823855</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="AC3">
-        <v>-0.4971611007047704</v>
+        <v>-0.4728041991400549</v>
       </c>
       <c r="AD3">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.292</v>
+        <v>-0.283</v>
       </c>
       <c r="AH3">
-        <v>0.1600454029511918</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.2577696526508227</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08568075117370892</v>
+        <v>-0.9496644295302012</v>
       </c>
       <c r="AK3">
-        <v>-0.1680092059838896</v>
+        <v>-0.1396151948692649</v>
       </c>
       <c r="AL3">
-        <v>0.034</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0.009000000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="AN3">
-        <v>-0.7572502685284639</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-27.8235294117647</v>
+        <v>-430.5</v>
       </c>
       <c r="AP3">
-        <v>0.313641245972073</v>
+        <v>0.3298368298368298</v>
       </c>
       <c r="AQ3">
-        <v>-105.1111111111111</v>
+        <v>-861</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Conferize A/S (CPSE:CONFRZ)</t>
+          <t>Seluxit A/S (CPSE:SLXIT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,23 +843,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0167</v>
+      </c>
       <c r="G4">
-        <v>-91.83333333333331</v>
+        <v>-0.5945454545454544</v>
       </c>
       <c r="H4">
-        <v>-148.3333333333333</v>
+        <v>-1.072727272727273</v>
       </c>
       <c r="I4">
-        <v>-108.3333333333333</v>
+        <v>-1.081818181818182</v>
       </c>
       <c r="J4">
-        <v>-108.3333333333333</v>
+        <v>-1.081818181818182</v>
       </c>
       <c r="K4">
-        <v>-1.3</v>
+        <v>-0.885</v>
       </c>
       <c r="L4">
-        <v>-108.3333333333333</v>
+        <v>-0.8045454545454545</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.909</v>
+        <v>0.403</v>
       </c>
       <c r="V4">
-        <v>0.7703389830508475</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="W4">
-        <v>-0.3403141361256545</v>
+        <v>-0.4359605911330049</v>
       </c>
       <c r="X4">
-        <v>0.1136433898635046</v>
+        <v>0.1146761330844727</v>
       </c>
       <c r="Y4">
-        <v>-0.4539575259891591</v>
+        <v>-0.5506367242174777</v>
       </c>
       <c r="Z4">
-        <v>0.007643312101910829</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="AA4">
-        <v>-0.8280254777070065</v>
+        <v>-0.6846950517836593</v>
       </c>
       <c r="AB4">
-        <v>0.1136433898635046</v>
+        <v>0.0942226033025606</v>
       </c>
       <c r="AC4">
-        <v>-0.941668867570511</v>
+        <v>-0.7789176550862199</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AG4">
-        <v>-0.909</v>
+        <v>0.322</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2804642166344294</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.370843989769821</v>
       </c>
       <c r="AJ4">
-        <v>-3.354243542435426</v>
+        <v>0.1475710357470211</v>
       </c>
       <c r="AK4">
-        <v>-0.3967699694456568</v>
+        <v>0.2074742268041237</v>
       </c>
       <c r="AL4">
-        <v>0.013</v>
+        <v>0.059</v>
       </c>
       <c r="AM4">
-        <v>0.013</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>-0.614406779661017</v>
       </c>
       <c r="AO4">
-        <v>-100</v>
+        <v>-20.16949152542373</v>
       </c>
       <c r="AP4">
-        <v>0.6992307692307692</v>
+        <v>-0.2728813559322034</v>
       </c>
       <c r="AQ4">
-        <v>-100</v>
+        <v>-31.31578947368422</v>
       </c>
     </row>
   </sheetData>
